--- a/respaldo-nexo.xlsx
+++ b/respaldo-nexo.xlsx
@@ -18287,7 +18287,7 @@
     <t>ZAPATOS Y SANDALIAS VIC GR</t>
   </si>
   <si>
-    <t>Ventas (2026-09-01 a 2026-09-10)</t>
+    <t>Ventas (2026-09-01 a 2026-09-11)</t>
   </si>
   <si>
     <t>Stock</t>
@@ -22189,7 +22189,7 @@
         <v>421</v>
       </c>
       <c r="E206">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -22206,7 +22206,7 @@
         <v>421</v>
       </c>
       <c r="E207">
-        <v>346</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -22223,7 +22223,7 @@
         <v>421</v>
       </c>
       <c r="E208">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -23090,7 +23090,7 @@
         <v>198</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -23226,7 +23226,7 @@
         <v>198</v>
       </c>
       <c r="E267">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
@@ -23260,7 +23260,7 @@
         <v>198</v>
       </c>
       <c r="E269">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
@@ -23294,7 +23294,7 @@
         <v>198</v>
       </c>
       <c r="E271">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
@@ -23872,7 +23872,7 @@
         <v>198</v>
       </c>
       <c r="E305">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -24178,7 +24178,7 @@
         <v>18</v>
       </c>
       <c r="E323">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -25793,7 +25793,7 @@
         <v>18</v>
       </c>
       <c r="E418">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -25878,7 +25878,7 @@
         <v>8</v>
       </c>
       <c r="E423">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -28819,7 +28819,7 @@
         <v>421</v>
       </c>
       <c r="E596">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -29142,7 +29142,7 @@
         <v>421</v>
       </c>
       <c r="E615">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
@@ -29278,7 +29278,7 @@
         <v>421</v>
       </c>
       <c r="E623">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
@@ -29295,7 +29295,7 @@
         <v>421</v>
       </c>
       <c r="E624">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -29346,7 +29346,7 @@
         <v>421</v>
       </c>
       <c r="E627">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -29499,7 +29499,7 @@
         <v>18</v>
       </c>
       <c r="E636">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
@@ -29635,7 +29635,7 @@
         <v>18</v>
       </c>
       <c r="E644">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -29941,7 +29941,7 @@
         <v>421</v>
       </c>
       <c r="E662">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -30298,7 +30298,7 @@
         <v>18</v>
       </c>
       <c r="E683">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -30315,7 +30315,7 @@
         <v>18</v>
       </c>
       <c r="E684">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -30808,7 +30808,7 @@
         <v>421</v>
       </c>
       <c r="E713">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
@@ -31284,7 +31284,7 @@
         <v>18</v>
       </c>
       <c r="E741">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
@@ -31658,7 +31658,7 @@
         <v>18</v>
       </c>
       <c r="E763">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.25">
@@ -31862,7 +31862,7 @@
         <v>41</v>
       </c>
       <c r="E775">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.25">
@@ -33324,7 +33324,7 @@
         <v>85</v>
       </c>
       <c r="E861">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.25">
@@ -34276,7 +34276,7 @@
         <v>421</v>
       </c>
       <c r="E917">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="918" spans="1:5" x14ac:dyDescent="0.25">
@@ -34293,7 +34293,7 @@
         <v>421</v>
       </c>
       <c r="E918">
-        <v>266</v>
+        <v>228</v>
       </c>
     </row>
     <row r="919" spans="1:5" x14ac:dyDescent="0.25">
@@ -34888,7 +34888,7 @@
         <v>421</v>
       </c>
       <c r="E953">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="954" spans="1:5" x14ac:dyDescent="0.25">
@@ -35517,7 +35517,7 @@
         <v>198</v>
       </c>
       <c r="E990">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="991" spans="1:5" x14ac:dyDescent="0.25">
@@ -37115,7 +37115,7 @@
         <v>198</v>
       </c>
       <c r="E1084">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
@@ -37149,7 +37149,7 @@
         <v>198</v>
       </c>
       <c r="E1086">
-        <v>384</v>
+        <v>336</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
@@ -37268,7 +37268,7 @@
         <v>198</v>
       </c>
       <c r="E1093">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
@@ -37421,7 +37421,7 @@
         <v>198</v>
       </c>
       <c r="E1102">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
@@ -37455,7 +37455,7 @@
         <v>198</v>
       </c>
       <c r="E1104">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
@@ -37472,7 +37472,7 @@
         <v>198</v>
       </c>
       <c r="E1105">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
@@ -37523,7 +37523,7 @@
         <v>198</v>
       </c>
       <c r="E1108">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
@@ -37659,7 +37659,7 @@
         <v>198</v>
       </c>
       <c r="E1116">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
@@ -37880,7 +37880,7 @@
         <v>198</v>
       </c>
       <c r="E1129">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
@@ -37914,7 +37914,7 @@
         <v>198</v>
       </c>
       <c r="E1131">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1132" spans="1:5" x14ac:dyDescent="0.25">
@@ -37931,7 +37931,7 @@
         <v>198</v>
       </c>
       <c r="E1132">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1133" spans="1:5" x14ac:dyDescent="0.25">
@@ -38509,7 +38509,7 @@
         <v>198</v>
       </c>
       <c r="E1166">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1167" spans="1:5" x14ac:dyDescent="0.25">
@@ -38543,7 +38543,7 @@
         <v>198</v>
       </c>
       <c r="E1168">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1169" spans="1:5" x14ac:dyDescent="0.25">
@@ -38611,7 +38611,7 @@
         <v>198</v>
       </c>
       <c r="E1172">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
@@ -38628,7 +38628,7 @@
         <v>93</v>
       </c>
       <c r="E1173">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1174" spans="1:5" x14ac:dyDescent="0.25">
@@ -40668,7 +40668,7 @@
         <v>8</v>
       </c>
       <c r="E1293">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1294" spans="1:5" x14ac:dyDescent="0.25">
@@ -44850,7 +44850,7 @@
         <v>8</v>
       </c>
       <c r="E1539">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1540" spans="1:5" x14ac:dyDescent="0.25">
@@ -50392,7 +50392,7 @@
         <v>8</v>
       </c>
       <c r="E1865">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1866" spans="1:5" x14ac:dyDescent="0.25">
@@ -51548,7 +51548,7 @@
         <v>421</v>
       </c>
       <c r="E1933">
-        <v>353</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1934" spans="1:5" x14ac:dyDescent="0.25">
@@ -55492,7 +55492,7 @@
         <v>8</v>
       </c>
       <c r="E2165">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2166" spans="1:5" x14ac:dyDescent="0.25">
@@ -60286,7 +60286,7 @@
         <v>18</v>
       </c>
       <c r="E2447">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2448" spans="1:5" x14ac:dyDescent="0.25">
@@ -61034,7 +61034,7 @@
         <v>18</v>
       </c>
       <c r="E2491">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2492" spans="1:5" x14ac:dyDescent="0.25">
